--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Maps Open Nursing Core clinical findings to NANDA-I Nursing Diagnoses.</t>
+    <t>Maps Open Nursing Core clinical findings to NANDA-I Nursing Diagnoses. NOT PRODUCTION-READY: see the placeholder-canonical note below.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,7 +93,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/nanda-i</t>
+    <t>https://opennursingcoreig.com/CodeSystem/nanda-i-PLACEHOLDER</t>
   </si>
   <si>
     <t>Display</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Risk for Loneliness</t>
   </si>
   <si>
-    <t>skintone-observation</t>
+    <t>mst-score</t>
   </si>
   <si>
     <t>source-is-broader-than-target</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/onc-to-nanda.xlsx
+++ b/onc-to-nanda.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
